--- a/assets/docs/lop3/Tieng Anh - Lop 3.xlsx
+++ b/assets/docs/lop3/Tieng Anh - Lop 3.xlsx
@@ -553,7 +553,7 @@
       </c>
       <c r="H4" s="4" t="inlineStr">
         <is>
-          <t>Digital competence 1.1 CB1b: Pupils look at the e-book on the TV, point out the Units and Lessons and say the name of the part they are going to learn.</t>
+          <t>Digital Competence (1.1CB1a): Identify information needs about the subject (units, lessons, icons) through the use of e-books and presentation slides.</t>
         </is>
       </c>
     </row>
@@ -1532,7 +1532,7 @@
       <c r="H32" s="4" t="inlineStr">
         <is>
           <t>Digital competence Domain 1 (Basic, level 1): To start Unit 5 My hobbies, the teacher shows a set of hobby pictures with model audio files; pupils listen, then match the names of the hobbies with the pictures
-Digital competence Domain 2 (Basic, level 1): The teacher shows the class survey table of hobbies; each pair asks and answers in English and then reads out the answers for the teacher to tick in the table
+Digital competence Domain 2 (Basic, level 1): T displays a class hobby survey table; pairs ask and answer and T ticks their answers; the class says a sentence about the most popular hobby
 Life skills: Communication skills: confidently greet others and introduce themselves in simple sentences.</t>
         </is>
       </c>
